--- a/public/post/drafts/season-prediction/men_breakthrough_predictor-selection-results.xlsx
+++ b/public/post/drafts/season-prediction/men_breakthrough_predictor-selection-results.xlsx
@@ -29,76 +29,76 @@
     <t xml:space="preserve">Avg_Importance</t>
   </si>
   <si>
+    <t xml:space="preserve">Prev_Pct_of_Max_Points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43608312530706</t>
+  </si>
+  <si>
     <t xml:space="preserve">Age</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06752055982879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33510702705174</t>
+    <t xml:space="preserve">1.00121097227135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Sprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.188435580861674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0929271603640194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0772344312928795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Sprint_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0564310295751208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.133615002708437</t>
   </si>
   <si>
     <t xml:space="preserve">Exp</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286542998820637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.197113539497547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0609414787851638</t>
+    <t xml:space="preserve">-0.29673648486483</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Pelo</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.300537847352177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Distance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.428380485302584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Sprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.495451328434632</t>
+    <t xml:space="preserve">-0.404273363867886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Distance_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.533836692919785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Sprint_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.590571840888783</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Distance_C</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.64016745996356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Distance_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.678104633298854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Sprint_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.695126515008158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Sprint_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.709457334623903</t>
+    <t xml:space="preserve">-0.780426855272144</t>
   </si>
   <si>
     <t xml:space="preserve">Model</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">                         Estimate Std. Error z value Pr(&gt;|z|)    </t>
   </si>
   <si>
-    <t xml:space="preserve">(Intercept)            -13.442663   3.363213  -3.997 6.42e-05 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age                     -0.166193   0.064573  -2.574 0.010061 *  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points   2.240117   1.474600   1.519 0.128728    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exp                      0.004832   0.003723   1.298 0.194361    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_F                   0.001934   0.002083   0.929 0.353056    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_C                   0.006744   0.002013   3.350 0.000808 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual deviance: 429.35  on 6143  degrees of freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIC: 441.35</t>
+    <t xml:space="preserve">(Intercept)            -1.566e+01  2.886e+00  -5.424 5.83e-08 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Pct_of_Max_Points  2.531e+00  1.466e+00   1.727  0.08424 .  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age                    -1.063e-01  4.749e-02  -2.239  0.02514 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Sprint             2.582e-04  1.283e-03   0.201  0.84050    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_C                  6.813e-03  2.093e-03   3.254  0.00114 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_F                  2.306e-03  2.148e-03   1.073  0.28306    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual deviance: 430.96  on 6143  degrees of freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIC: 442.96</t>
   </si>
   <si>
     <t xml:space="preserve">Number of Fisher Scoring iterations: 8</t>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
+        <v>40.1793780633852</v>
+      </c>
+      <c r="C2" t="n">
         <v>100</v>
-      </c>
-      <c r="C2" t="n">
-        <v>75.5183871491534</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -580,10 +580,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>40.1793780633852</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>17.543204319491</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -594,10 +594,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>50.3120509768786</v>
+        <v>22.8392517141522</v>
       </c>
       <c r="C4" t="n">
-        <v>27.9708098060598</v>
+        <v>52.6703926493993</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -608,10 +608,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>31.1114046112393</v>
+        <v>17.8894651494085</v>
       </c>
       <c r="C5" t="n">
-        <v>44.260470702118</v>
+        <v>52.6749004507435</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -622,10 +622,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>17.8894651494085</v>
+        <v>31.1114046112393</v>
       </c>
       <c r="C6" t="n">
-        <v>51.1599299383137</v>
+        <v>38.6201080860267</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -636,10 +636,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>22.6888838411559</v>
+        <v>23.7588264000277</v>
       </c>
       <c r="C7" t="n">
-        <v>24.8682935292974</v>
+        <v>39.0523101472982</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -653,7 +653,7 @@
         <v>21.7648293595918</v>
       </c>
       <c r="C8" t="n">
-        <v>18.5006776846343</v>
+        <v>37.0469374096567</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -664,10 +664,10 @@
         <v>18</v>
       </c>
       <c r="B9" t="n">
-        <v>22.8392517141522</v>
+        <v>50.3120509768786</v>
       </c>
       <c r="C9" t="n">
-        <v>13.4167672072474</v>
+        <v>0</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -678,10 +678,10 @@
         <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>18.9205456413785</v>
+        <v>22.6888838411559</v>
       </c>
       <c r="C10" t="n">
-        <v>9.42043112939047</v>
+        <v>22.0869775060957</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
@@ -695,7 +695,7 @@
         <v>5.99672309603337</v>
       </c>
       <c r="C11" t="n">
-        <v>21.6733427649972</v>
+        <v>32.0849852212473</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>27.3924031719569</v>
+        <v>35.1484721168207</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -720,10 +720,10 @@
         <v>26</v>
       </c>
       <c r="B13" t="n">
-        <v>23.7588264000277</v>
+        <v>18.9205456413785</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>6.355913793724</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -756,7 +756,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="n">
-        <v>0.918052823315118</v>
+        <v>0.911690346083789</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
@@ -767,7 +767,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>0.91387795992714</v>
+        <v>0.918100182149363</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>

--- a/public/post/drafts/season-prediction/men_breakthrough_predictor-selection-results.xlsx
+++ b/public/post/drafts/season-prediction/men_breakthrough_predictor-selection-results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">Predictor</t>
   </si>
@@ -29,76 +29,76 @@
     <t xml:space="preserve">Avg_Importance</t>
   </si>
   <si>
+    <t xml:space="preserve">Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30154282694938</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prev_Pct_of_Max_Points</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43608312530706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00121097227135</t>
+    <t xml:space="preserve">1.25885056321162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487049000736862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.134732003173069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.165397021405017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Sprint_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.238149589825447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Pelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.418331989070771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.466409757469413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Distance_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.550438531680776</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Sprint</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188435580861674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0929271603640194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0772344312928795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Sprint_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0564310295751208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Distance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.133615002708437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.29673648486483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Pelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.404273363867886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Distance_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.533836692919785</t>
+    <t xml:space="preserve">-0.626726303950973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Distance_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.677637820904504</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Sprint_F</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.590571840888783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Distance_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.780426855272144</t>
+    <t xml:space="preserve">-0.769619373417891</t>
   </si>
   <si>
     <t xml:space="preserve">Model</t>
@@ -191,31 +191,25 @@
     <t xml:space="preserve">Number of Fisher Scoring iterations: 9</t>
   </si>
   <si>
-    <t xml:space="preserve">                         Estimate Std. Error z value Pr(&gt;|z|)    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Intercept)            -1.566e+01  2.886e+00  -5.424 5.83e-08 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points  2.531e+00  1.466e+00   1.727  0.08424 .  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age                    -1.063e-01  4.749e-02  -2.239  0.02514 *  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Sprint             2.582e-04  1.283e-03   0.201  0.84050    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_C                  6.813e-03  2.093e-03   3.254  0.00114 ** </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_F                  2.306e-03  2.148e-03   1.073  0.28306    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual deviance: 430.96  on 6143  degrees of freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIC: 442.96</t>
+    <t xml:space="preserve">                        Estimate Std. Error z value Pr(&gt;|z|)    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)            -2.586356   1.476177  -1.752   0.0798 .  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age                    -0.152209   0.063357  -2.402   0.0163 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Pct_of_Max_Points  6.716495   0.825630   8.135 4.12e-16 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exp                     0.007736   0.003549   2.180   0.0293 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual deviance: 444.37  on 6145  degrees of freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIC: 452.37</t>
   </si>
   <si>
     <t xml:space="preserve">Number of Fisher Scoring iterations: 8</t>
@@ -566,10 +560,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>40.1793780633852</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>92.7370924679662</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -580,10 +574,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
+        <v>40.1793780633852</v>
+      </c>
+      <c r="C3" t="n">
         <v>100</v>
-      </c>
-      <c r="C3" t="n">
-        <v>17.543204319491</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -594,10 +588,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>22.8392517141522</v>
+        <v>50.3120509768786</v>
       </c>
       <c r="C4" t="n">
-        <v>52.6703926493993</v>
+        <v>37.6086596631501</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -608,10 +602,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>17.8894651494085</v>
+        <v>31.1114046112393</v>
       </c>
       <c r="C5" t="n">
-        <v>52.6749004507435</v>
+        <v>21.4249616017662</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -622,10 +616,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>31.1114046112393</v>
+        <v>17.8894651494085</v>
       </c>
       <c r="C6" t="n">
-        <v>38.6201080860267</v>
+        <v>35.9147134562173</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -639,7 +633,7 @@
         <v>23.7588264000277</v>
       </c>
       <c r="C7" t="n">
-        <v>39.0523101472982</v>
+        <v>23.913081668911</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -650,10 +644,10 @@
         <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>21.7648293595918</v>
+        <v>22.6888838411559</v>
       </c>
       <c r="C8" t="n">
-        <v>37.0469374096567</v>
+        <v>13.6261174995445</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -664,10 +658,10 @@
         <v>18</v>
       </c>
       <c r="B9" t="n">
-        <v>50.3120509768786</v>
+        <v>21.7648293595918</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>11.6765629385819</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -678,10 +672,10 @@
         <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>22.6888838411559</v>
+        <v>5.99672309603337</v>
       </c>
       <c r="C10" t="n">
-        <v>22.0869775060957</v>
+        <v>25.8961395183758</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
@@ -692,10 +686,10 @@
         <v>22</v>
       </c>
       <c r="B11" t="n">
-        <v>5.99672309603337</v>
+        <v>22.8392517141522</v>
       </c>
       <c r="C11" t="n">
-        <v>32.0849852212473</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -706,10 +700,10 @@
         <v>24</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>18.9205456413785</v>
       </c>
       <c r="C12" t="n">
-        <v>35.1484721168207</v>
+        <v>1.59739265129299</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -720,10 +714,10 @@
         <v>26</v>
       </c>
       <c r="B13" t="n">
-        <v>18.9205456413785</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>6.355913793724</v>
+        <v>19.2303194772115</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -756,7 +750,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="n">
-        <v>0.911690346083789</v>
+        <v>0.912837887067395</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
@@ -767,10 +761,10 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>0.918100182149363</v>
+        <v>0.916663023679417</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -997,22 +991,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -1022,41 +1016,31 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
         <v>33</v>
       </c>
     </row>
